--- a/Results/lica_placebo_INTERNAL_VALIDATION_SUMMARY.xlsx
+++ b/Results/lica_placebo_INTERNAL_VALIDATION_SUMMARY.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Age, Onset_Limb, Sex_Male, Diagnostic_Delay, Age_sq</t>
+          <t>Age, Onset_Limb, Sex_Male, Diagnostic_Delay, Age_Sex</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -488,7 +488,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>902.812</t>
+          <t>289.369</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>0.815</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.674</t>
+          <t>0.746</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[0.318, 0.692]</t>
+          <t>[0.727, 0.804]</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.986</t>
+          <t>0.998</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -556,12 +556,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.825</t>
+          <t>0.654</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[-0.964, 1.038]</t>
+          <t>[0.468, 0.791]</t>
         </is>
       </c>
     </row>
@@ -571,12 +571,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CITL at 20 months (apparent, best model)</t>
+          <t>CITL at 25 months (apparent, best model)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.225</t>
+          <t>-0.236</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -587,17 +587,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CITL at 20 months (optimism-corrected, strategy)</t>
+          <t>CITL at 25 months (optimism-corrected, strategy)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.270</t>
+          <t>-0.524</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[-1.593, -0.989]</t>
+          <t>[-0.626, -0.091]</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -628,7 +628,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
